--- a/aq_files/0664.xlsx
+++ b/aq_files/0664.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="List_Methods" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,468 +413,783 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>Databases are optimized for:</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>append() does:</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A) add element B) remove C) sort D) none</t>
+          <t>OLTP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Batch processing</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ML training</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>Data warehouses are optimized for:</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pop() does:</t>
+          <t>OLTP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A) remove last B) add C) sort D) none</t>
+          <t>OLAP</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Caching</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>Databases store primarily:</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sort() does:</t>
+          <t>Historical data</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A) sort list B) reverse C) add D) none</t>
+          <t>Current transactional data</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Aggregates only</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Logs only</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>DW stores primarily:</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>len() gives:</t>
+          <t>Current data</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A) length B) type C) value D) none</t>
+          <t>Historical integrated data</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Temp data</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Cache</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Normalization is common in:</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Implement stack using list.</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Denormalization is common in:</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Implement queue using list.</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Complex analytical queries are best suited for:</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Reverse list using methods.</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Insert/update frequency is higher in:</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sort list without built-in.</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>DW refresh is typically:</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Remove duplicates using methods.</t>
+          <t>Real-time always</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>Periodic/batch</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Random</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Which uses star schema?</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Find kth largest element.</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Real-time transactions are handled by:</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rotate list using slicing.</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Aggregated data is typical of:</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Find median of list.</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Faster inserts are typical in:</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Merge lists and sort.</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Example relational DB:</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Find min difference between elements.</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>BigQuery</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Redshift</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>A banking system processes deposits and withdrawals in real-time. Which system?</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Check palindrome using list.</t>
+          <t>Data warehouse</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>Database (OLTP)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Cache</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data lake</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>A company runs monthly revenue reports across years. Which system?</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Simulate push/pop operations.</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>Data warehouse</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Cache</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Search engine</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Need strict normalization to avoid anomalies. Choose:</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Find frequency using list.</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Need fast analytics with fewer joins via denormalized tables. Choose:</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Find sum of subarrays.</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>High-frequency writes with ACID transactions. Choose:</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Reverse list segments.</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Ad-hoc queries over historical data at scale. Choose:</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Find sliding window max.</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
